--- a/Output/descriptive.xlsx
+++ b/Output/descriptive.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10402"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uccl0.sharepoint.com/sites/sh365_LABPSICOSOCIAL/Documentos compartidos/General/LAB Studies/Current work/ELRI/Escritura/Intergroup Trust/Análisis/PosxNeg Intergroup trust/Output/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="11_3DAB9CC08F79A8836D3E7CD2E17BD2728ACFC9C4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F8E0CD61-BF14-4415-9B11-6E68DAA1714B}"/>
+  <xr:revisionPtr revIDLastSave="29" documentId="11_3DAB9CC08F79A8836D3E7CD2E17BD2728ACFC9C4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A3B8C26-3BD1-584A-9440-46A158DA1403}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-30140" yWindow="1800" windowWidth="21800" windowHeight="12980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -635,12 +635,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16.06640625" customWidth="1"/>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="5" max="5" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>78</v>
       </c>
@@ -665,7 +666,7 @@
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -706,7 +707,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>79</v>
       </c>
@@ -723,7 +724,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -752,7 +753,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -781,7 +782,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>80</v>
       </c>
@@ -822,7 +823,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>82</v>
       </c>
@@ -863,7 +864,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>81</v>
       </c>
@@ -880,7 +881,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>83</v>
       </c>
@@ -909,7 +910,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>84</v>
       </c>
@@ -938,7 +939,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>85</v>
       </c>
@@ -979,7 +980,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>86</v>
       </c>
@@ -1020,7 +1021,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>87</v>
       </c>
@@ -1061,7 +1062,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>88</v>
       </c>
@@ -1102,7 +1103,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>89</v>
       </c>
@@ -1155,8 +1156,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100B2A3E0705DA085419D287A2DA5101C7B" ma:contentTypeVersion="14" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="dd58eb11a06c7e24b05b443bdc164aea">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f69ae86b-b091-4d61-b03f-36bd36a91ba7" xmlns:ns3="d650c2d9-a7d7-4194-ba53-53a0dd7160ef" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9f695f40ee278d469e2ba2df0d63cd1e" ns2:_="" ns3:_="">
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B2A3E0705DA085419D287A2DA5101C7B" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c0cd21772f2dd4feec5af7bd7f00ee5b">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f69ae86b-b091-4d61-b03f-36bd36a91ba7" xmlns:ns3="d650c2d9-a7d7-4194-ba53-53a0dd7160ef" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8bea9126bb8fd557d945ac7777fcee8c" ns2:_="" ns3:_="">
     <xsd:import namespace="f69ae86b-b091-4d61-b03f-36bd36a91ba7"/>
     <xsd:import namespace="d650c2d9-a7d7-4194-ba53-53a0dd7160ef"/>
     <xsd:element name="properties">
@@ -1228,7 +1238,7 @@
         <xsd:restriction base="dms:Unknown"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="17" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de imagen" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="cc44c076-1990-432d-b910-f78c9fed31bd" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="17" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="cc44c076-1990-432d-b910-f78c9fed31bd" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
@@ -1277,8 +1287,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de contenido"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -1367,15 +1377,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1388,13 +1389,30 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F889E8C8-55C7-4AFB-A6A6-8706B6D40FF6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F781A92E-2482-4531-BDA0-1A55F9F1835E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F781A92E-2482-4531-BDA0-1A55F9F1835E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4526212-1220-4C4A-8F8F-416A9CC701A3}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F86C6AF-ABE4-4433-BB3A-B287682F2B1C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F86C6AF-ABE4-4433-BB3A-B287682F2B1C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="f69ae86b-b091-4d61-b03f-36bd36a91ba7"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="d650c2d9-a7d7-4194-ba53-53a0dd7160ef"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Output/descriptive.xlsx
+++ b/Output/descriptive.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10402"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="29" documentId="11_3DAB9CC08F79A8836D3E7CD2E17BD2728ACFC9C4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A3B8C26-3BD1-584A-9440-46A158DA1403}"/>
   <bookViews>
-    <workbookView xWindow="-30140" yWindow="1800" windowWidth="21800" windowHeight="12980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -635,13 +635,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="5" max="5" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>78</v>
       </c>
@@ -666,7 +666,7 @@
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -707,7 +707,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>79</v>
       </c>
@@ -724,7 +724,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -753,7 +753,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -782,7 +782,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>80</v>
       </c>
@@ -823,7 +823,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>82</v>
       </c>
@@ -864,7 +864,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>81</v>
       </c>
@@ -881,7 +881,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>83</v>
       </c>
@@ -910,7 +910,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>84</v>
       </c>
@@ -939,7 +939,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>85</v>
       </c>
@@ -980,7 +980,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>86</v>
       </c>
@@ -1021,7 +1021,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>87</v>
       </c>
@@ -1062,7 +1062,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>88</v>
       </c>
@@ -1103,7 +1103,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>89</v>
       </c>
@@ -1156,17 +1156,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B2A3E0705DA085419D287A2DA5101C7B" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c0cd21772f2dd4feec5af7bd7f00ee5b">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f69ae86b-b091-4d61-b03f-36bd36a91ba7" xmlns:ns3="d650c2d9-a7d7-4194-ba53-53a0dd7160ef" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8bea9126bb8fd557d945ac7777fcee8c" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100B2A3E0705DA085419D287A2DA5101C7B" ma:contentTypeVersion="14" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="b2430ed3a4ec7f257ca04f80e9e7b7d0">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f69ae86b-b091-4d61-b03f-36bd36a91ba7" xmlns:ns3="d650c2d9-a7d7-4194-ba53-53a0dd7160ef" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="219b602c7c743fe11b4baf9954089a3e" ns2:_="" ns3:_="">
     <xsd:import namespace="f69ae86b-b091-4d61-b03f-36bd36a91ba7"/>
     <xsd:import namespace="d650c2d9-a7d7-4194-ba53-53a0dd7160ef"/>
     <xsd:element name="properties">
@@ -1238,7 +1229,7 @@
         <xsd:restriction base="dms:Unknown"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="17" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="cc44c076-1990-432d-b910-f78c9fed31bd" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="17" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de imagen" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="cc44c076-1990-432d-b910-f78c9fed31bd" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
@@ -1287,8 +1278,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de contenido"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -1377,6 +1368,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1389,15 +1389,15 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD71542B-AA96-4C0C-B381-4870D8CCD6DB}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F781A92E-2482-4531-BDA0-1A55F9F1835E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4526212-1220-4C4A-8F8F-416A9CC701A3}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
